--- a/PROPERTIES/BORDER BUSINESS CENTER/BOADER BUSINESS CENTRE2025.xlsx
+++ b/PROPERTIES/BORDER BUSINESS CENTER/BOADER BUSINESS CENTRE2025.xlsx
@@ -1727,7 +1727,7 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="43" width="17.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="43" width="25.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="43" width="34.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="43" width="17.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="43" width="22.88"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="43" width="14.67"/>

--- a/PROPERTIES/BORDER BUSINESS CENTER/BOADER BUSINESS CENTRE2025.xlsx
+++ b/PROPERTIES/BORDER BUSINESS CENTER/BOADER BUSINESS CENTRE2025.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="JUNE" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="JULY" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="AUG" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="63">
   <si>
     <t xml:space="preserve">TEL: 0703759351 / 0723575686</t>
   </si>
@@ -198,6 +199,18 @@
   </si>
   <si>
     <t xml:space="preserve">TG728013Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📞 paid to Kevin,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📞</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH23ITADOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📞 on 6/8/25</t>
   </si>
 </sst>
 </file>
@@ -216,7 +229,7 @@
     <numFmt numFmtId="172" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="173" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,6 +379,14 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -432,7 +453,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -798,6 +819,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2461,4 +2486,626 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J38"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="43" width="17.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="43" width="34.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="43" width="17.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="43" width="22.88"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="43" width="14.67"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="43" width="12.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="43" width="39.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="43" width="17.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="43" width="27.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="43" width="24.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24.56"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="44"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+    </row>
+    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="44"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="45"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="52" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="54" t="n">
+        <v>723438116</v>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E6" s="55" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F6" s="56"/>
+      <c r="G6" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="53"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="54" t="n">
+        <v>720214783</v>
+      </c>
+      <c r="D7" s="55" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E7" s="55"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="57" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="49"/>
+      <c r="I7" s="53"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="54" t="n">
+        <v>746341384</v>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E8" s="55" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F8" s="56"/>
+      <c r="G8" s="57" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H8" s="49"/>
+      <c r="I8" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="58" t="n">
+        <v>45696</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="54" t="n">
+        <v>725998678</v>
+      </c>
+      <c r="D9" s="55" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E9" s="55"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="57" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="49"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="58"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="54" t="n">
+        <v>745458044</v>
+      </c>
+      <c r="D10" s="55" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E10" s="59" t="n">
+        <v>22</v>
+      </c>
+      <c r="F10" s="60"/>
+      <c r="G10" s="57" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="49"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="58"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="43" t="n">
+        <v>725371652</v>
+      </c>
+      <c r="D11" s="55" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E11" s="61"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="53"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="44" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="54" t="n">
+        <v>745203974</v>
+      </c>
+      <c r="D12" s="55" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E12" s="55"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="49" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I12" s="53"/>
+      <c r="J12" s="63"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="54" t="n">
+        <v>702195722</v>
+      </c>
+      <c r="D13" s="55" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E13" s="55"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="64"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="65" t="n">
+        <v>712854747</v>
+      </c>
+      <c r="D14" s="55" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E14" s="55"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="66"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="65" t="n">
+        <v>712854747</v>
+      </c>
+      <c r="D15" s="55" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E15" s="55"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="66"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="67" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="68" t="n">
+        <v>704071266</v>
+      </c>
+      <c r="D16" s="69" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E16" s="69"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="70"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="67" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="68" t="n">
+        <v>701270976</v>
+      </c>
+      <c r="D17" s="69" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E17" s="69"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="57" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="62"/>
+      <c r="I17" s="52"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="44" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="54" t="n">
+        <v>728078440</v>
+      </c>
+      <c r="D18" s="55" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E18" s="55"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="71"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="67" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="66" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="67" t="n">
+        <v>790381810</v>
+      </c>
+      <c r="D19" s="72" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E19" s="67" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F19" s="67"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="74"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="75" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="67" t="n">
+        <v>790381810</v>
+      </c>
+      <c r="D20" s="77" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E20" s="77" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F20" s="78"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="74"/>
+    </row>
+    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="44" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="54" t="n">
+        <v>707608598</v>
+      </c>
+      <c r="D21" s="55" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E21" s="55"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="53"/>
+    </row>
+    <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="44" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="68" t="n">
+        <v>707608598</v>
+      </c>
+      <c r="D22" s="55" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E22" s="55"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="71"/>
+    </row>
+    <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="80" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="43" t="n">
+        <v>115169443</v>
+      </c>
+      <c r="D23" s="81" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E23" s="81"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="71"/>
+    </row>
+    <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="44" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="80" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="43" t="n">
+        <v>115169443</v>
+      </c>
+      <c r="D24" s="55" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E24" s="55"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="71"/>
+    </row>
+    <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="44" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="54" t="n">
+        <v>702756240</v>
+      </c>
+      <c r="D25" s="55" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E25" s="55"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="53"/>
+    </row>
+    <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="44"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="71"/>
+    </row>
+    <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="67"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="69" t="n">
+        <f aca="false">SUM(D6:D26)</f>
+        <v>350000</v>
+      </c>
+      <c r="E27" s="69"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="92" t="n">
+        <f aca="false">SUM(G6:G26)</f>
+        <v>20000</v>
+      </c>
+      <c r="H27" s="62"/>
+      <c r="I27" s="84"/>
+    </row>
+    <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="67"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="85"/>
+    </row>
+    <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="86"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="86"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="87"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="88"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="53"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="90"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="44"/>
+      <c r="C33" s="53"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="44"/>
+      <c r="C34" s="53"/>
+      <c r="F34" s="91"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A29:C29"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/PROPERTIES/BORDER BUSINESS CENTER/BOADER BUSINESS CENTRE2025.xlsx
+++ b/PROPERTIES/BORDER BUSINESS CENTER/BOADER BUSINESS CENTRE2025.xlsx
@@ -201,13 +201,13 @@
     <t xml:space="preserve">TG728013Y</t>
   </si>
   <si>
-    <t xml:space="preserve">📞 paid to Kevin,</t>
-  </si>
-  <si>
     <t xml:space="preserve">📞</t>
   </si>
   <si>
     <t xml:space="preserve">TH23ITADOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMMARY</t>
   </si>
   <si>
     <t xml:space="preserve">📞 on 6/8/25</t>
@@ -229,7 +229,7 @@
     <numFmt numFmtId="172" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="173" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -381,6 +381,22 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="13"/>
       <color rgb="FF008000"/>
       <name val="Georgia"/>
@@ -453,7 +469,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="96">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -822,7 +838,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2493,7 +2521,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="43" width="17.56"/>
@@ -2506,7 +2534,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="43" width="17.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="43" width="27.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="43" width="24.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="92" width="24.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2560,6 +2588,7 @@
       <c r="G4" s="48"/>
       <c r="H4" s="49"/>
       <c r="I4" s="49"/>
+      <c r="K4" s="93"/>
     </row>
     <row r="5" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="45" t="s">
@@ -2592,6 +2621,9 @@
       <c r="J5" s="52" t="s">
         <v>43</v>
       </c>
+      <c r="K5" s="52" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="44" t="n">
@@ -2610,10 +2642,11 @@
         <v>20000</v>
       </c>
       <c r="F6" s="56"/>
-      <c r="G6" s="57" t="s">
-        <v>59</v>
+      <c r="G6" s="57" t="n">
+        <v>20000</v>
       </c>
       <c r="I6" s="53"/>
+      <c r="K6" s="93"/>
     </row>
     <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="44" t="n">
@@ -2631,10 +2664,11 @@
       <c r="E7" s="55"/>
       <c r="F7" s="56"/>
       <c r="G7" s="57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H7" s="49"/>
       <c r="I7" s="53"/>
+      <c r="K7" s="93"/>
     </row>
     <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="44" t="n">
@@ -2658,11 +2692,12 @@
       </c>
       <c r="H8" s="49"/>
       <c r="I8" s="53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J8" s="58" t="n">
         <v>45696</v>
       </c>
+      <c r="K8" s="93"/>
     </row>
     <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="44" t="n">
@@ -2680,11 +2715,12 @@
       <c r="E9" s="55"/>
       <c r="F9" s="56"/>
       <c r="G9" s="57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H9" s="49"/>
       <c r="I9" s="53"/>
       <c r="J9" s="58"/>
+      <c r="K9" s="93"/>
     </row>
     <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="44" t="n">
@@ -2704,11 +2740,12 @@
       </c>
       <c r="F10" s="60"/>
       <c r="G10" s="57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H10" s="49"/>
       <c r="I10" s="53"/>
       <c r="J10" s="58"/>
+      <c r="K10" s="93"/>
     </row>
     <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="44" t="n">
@@ -2728,6 +2765,7 @@
       <c r="G11" s="57"/>
       <c r="H11" s="55"/>
       <c r="I11" s="53"/>
+      <c r="K11" s="93"/>
     </row>
     <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="n">
@@ -2744,12 +2782,15 @@
       </c>
       <c r="E12" s="55"/>
       <c r="F12" s="60"/>
-      <c r="G12" s="57"/>
+      <c r="G12" s="57" t="n">
+        <v>17000</v>
+      </c>
       <c r="H12" s="49" t="n">
         <v>3200</v>
       </c>
       <c r="I12" s="53"/>
       <c r="J12" s="63"/>
+      <c r="K12" s="93"/>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="n">
@@ -2770,6 +2811,9 @@
       <c r="H13" s="49"/>
       <c r="I13" s="53"/>
       <c r="J13" s="64"/>
+      <c r="K13" s="94" t="n">
+        <v>20000</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="44" t="n">
@@ -2786,9 +2830,12 @@
       </c>
       <c r="E14" s="55"/>
       <c r="F14" s="56"/>
-      <c r="G14" s="57"/>
+      <c r="G14" s="57" t="n">
+        <v>20000</v>
+      </c>
       <c r="H14" s="49"/>
       <c r="I14" s="66"/>
+      <c r="K14" s="93"/>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="44" t="n">
@@ -2805,9 +2852,12 @@
       </c>
       <c r="E15" s="55"/>
       <c r="F15" s="56"/>
-      <c r="G15" s="57"/>
+      <c r="G15" s="57" t="n">
+        <v>20000</v>
+      </c>
       <c r="H15" s="49"/>
       <c r="I15" s="66"/>
+      <c r="K15" s="93"/>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="67" t="n">
@@ -2827,6 +2877,7 @@
       <c r="G16" s="57"/>
       <c r="H16" s="62"/>
       <c r="I16" s="70"/>
+      <c r="K16" s="93"/>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="67" t="n">
@@ -2844,10 +2895,11 @@
       <c r="E17" s="69"/>
       <c r="F17" s="60"/>
       <c r="G17" s="57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H17" s="62"/>
       <c r="I17" s="52"/>
+      <c r="K17" s="93"/>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="44" t="n">
@@ -2867,6 +2919,7 @@
       <c r="G18" s="57"/>
       <c r="H18" s="49"/>
       <c r="I18" s="71"/>
+      <c r="K18" s="93"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="67" t="n">
@@ -2885,9 +2938,12 @@
         <v>15000</v>
       </c>
       <c r="F19" s="67"/>
-      <c r="G19" s="73"/>
+      <c r="G19" s="73" t="n">
+        <v>15000</v>
+      </c>
       <c r="H19" s="62"/>
       <c r="I19" s="74"/>
+      <c r="K19" s="93"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="75" t="n">
@@ -2906,9 +2962,12 @@
         <v>15000</v>
       </c>
       <c r="F20" s="78"/>
-      <c r="G20" s="79"/>
+      <c r="G20" s="79" t="n">
+        <v>15000</v>
+      </c>
       <c r="H20" s="49"/>
       <c r="I20" s="74"/>
+      <c r="K20" s="93"/>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="44" t="n">
@@ -2925,9 +2984,12 @@
       </c>
       <c r="E21" s="55"/>
       <c r="F21" s="56"/>
-      <c r="G21" s="57"/>
+      <c r="G21" s="57" t="n">
+        <v>15000</v>
+      </c>
       <c r="H21" s="49"/>
       <c r="I21" s="53"/>
+      <c r="K21" s="93"/>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="44" t="n">
@@ -2944,9 +3006,12 @@
       </c>
       <c r="E22" s="55"/>
       <c r="F22" s="56"/>
-      <c r="G22" s="57"/>
+      <c r="G22" s="57" t="n">
+        <v>15000</v>
+      </c>
       <c r="H22" s="49"/>
       <c r="I22" s="71"/>
+      <c r="K22" s="93"/>
     </row>
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="44" t="n">
@@ -2958,7 +3023,7 @@
       <c r="C23" s="43" t="n">
         <v>115169443</v>
       </c>
-      <c r="D23" s="81" t="n">
+      <c r="D23" s="55" t="n">
         <v>15000</v>
       </c>
       <c r="E23" s="81"/>
@@ -2966,6 +3031,7 @@
       <c r="G23" s="57"/>
       <c r="H23" s="49"/>
       <c r="I23" s="71"/>
+      <c r="K23" s="93"/>
     </row>
     <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="44" t="n">
@@ -2985,6 +3051,7 @@
       <c r="G24" s="57"/>
       <c r="H24" s="49"/>
       <c r="I24" s="71"/>
+      <c r="K24" s="93"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="44" t="n">
@@ -3001,9 +3068,12 @@
       </c>
       <c r="E25" s="55"/>
       <c r="F25" s="56"/>
-      <c r="G25" s="57"/>
+      <c r="G25" s="57" t="n">
+        <v>15000</v>
+      </c>
       <c r="H25" s="49"/>
       <c r="I25" s="53"/>
+      <c r="K25" s="93"/>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="44"/>
@@ -3015,6 +3085,7 @@
       <c r="G26" s="81"/>
       <c r="H26" s="49"/>
       <c r="I26" s="71"/>
+      <c r="K26" s="93"/>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="67"/>
@@ -3026,12 +3097,13 @@
       </c>
       <c r="E27" s="69"/>
       <c r="F27" s="60"/>
-      <c r="G27" s="92" t="n">
+      <c r="G27" s="95" t="n">
         <f aca="false">SUM(G6:G26)</f>
-        <v>20000</v>
+        <v>172000</v>
       </c>
       <c r="H27" s="62"/>
       <c r="I27" s="84"/>
+      <c r="K27" s="93"/>
     </row>
     <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="67"/>
@@ -3043,6 +3115,7 @@
       <c r="G28" s="83"/>
       <c r="H28" s="49"/>
       <c r="I28" s="85"/>
+      <c r="K28" s="93"/>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="86"/>
@@ -3058,7 +3131,7 @@
     </row>
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="43" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="E30" s="89" t="n">
         <v>0</v>

--- a/PROPERTIES/BORDER BUSINESS CENTER/BOADER BUSINESS CENTRE2025.xlsx
+++ b/PROPERTIES/BORDER BUSINESS CENTER/BOADER BUSINESS CENTRE2025.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="63">
   <si>
     <t xml:space="preserve">TEL: 0703759351 / 0723575686</t>
   </si>
@@ -2530,7 +2530,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="43" width="22.88"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="43" width="14.67"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="43" width="12.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="43" width="39.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="43" width="31.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="43" width="17.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="43" width="27.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="43" width="24.56"/>
@@ -2714,8 +2714,8 @@
       </c>
       <c r="E9" s="55"/>
       <c r="F9" s="56"/>
-      <c r="G9" s="57" t="s">
-        <v>59</v>
+      <c r="G9" s="57" t="n">
+        <v>20000</v>
       </c>
       <c r="H9" s="49"/>
       <c r="I9" s="53"/>
@@ -2739,8 +2739,8 @@
         <v>22</v>
       </c>
       <c r="F10" s="60"/>
-      <c r="G10" s="57" t="s">
-        <v>59</v>
+      <c r="G10" s="57" t="n">
+        <v>20200</v>
       </c>
       <c r="H10" s="49"/>
       <c r="I10" s="53"/>
@@ -2762,7 +2762,9 @@
       </c>
       <c r="E11" s="61"/>
       <c r="F11" s="62"/>
-      <c r="G11" s="57"/>
+      <c r="G11" s="57" t="n">
+        <v>20200</v>
+      </c>
       <c r="H11" s="55"/>
       <c r="I11" s="53"/>
       <c r="K11" s="93"/>
@@ -2807,7 +2809,9 @@
       </c>
       <c r="E13" s="55"/>
       <c r="F13" s="56"/>
-      <c r="G13" s="57"/>
+      <c r="G13" s="57" t="n">
+        <v>20000</v>
+      </c>
       <c r="H13" s="49"/>
       <c r="I13" s="53"/>
       <c r="J13" s="64"/>
@@ -2874,7 +2878,9 @@
       </c>
       <c r="E16" s="69"/>
       <c r="F16" s="60"/>
-      <c r="G16" s="57"/>
+      <c r="G16" s="57" t="n">
+        <v>15000</v>
+      </c>
       <c r="H16" s="62"/>
       <c r="I16" s="70"/>
       <c r="K16" s="93"/>
@@ -2894,9 +2900,7 @@
       </c>
       <c r="E17" s="69"/>
       <c r="F17" s="60"/>
-      <c r="G17" s="57" t="s">
-        <v>59</v>
-      </c>
+      <c r="G17" s="57"/>
       <c r="H17" s="62"/>
       <c r="I17" s="52"/>
       <c r="K17" s="93"/>
@@ -2939,7 +2943,7 @@
       </c>
       <c r="F19" s="67"/>
       <c r="G19" s="73" t="n">
-        <v>15000</v>
+        <v>15200</v>
       </c>
       <c r="H19" s="62"/>
       <c r="I19" s="74"/>
@@ -2963,7 +2967,7 @@
       </c>
       <c r="F20" s="78"/>
       <c r="G20" s="79" t="n">
-        <v>15000</v>
+        <v>15200</v>
       </c>
       <c r="H20" s="49"/>
       <c r="I20" s="74"/>
@@ -2985,7 +2989,7 @@
       <c r="E21" s="55"/>
       <c r="F21" s="56"/>
       <c r="G21" s="57" t="n">
-        <v>15000</v>
+        <v>15200</v>
       </c>
       <c r="H21" s="49"/>
       <c r="I21" s="53"/>
@@ -3007,7 +3011,7 @@
       <c r="E22" s="55"/>
       <c r="F22" s="56"/>
       <c r="G22" s="57" t="n">
-        <v>15000</v>
+        <v>15200</v>
       </c>
       <c r="H22" s="49"/>
       <c r="I22" s="71"/>
@@ -3028,7 +3032,9 @@
       </c>
       <c r="E23" s="81"/>
       <c r="F23" s="56"/>
-      <c r="G23" s="57"/>
+      <c r="G23" s="57" t="n">
+        <v>15250</v>
+      </c>
       <c r="H23" s="49"/>
       <c r="I23" s="71"/>
       <c r="K23" s="93"/>
@@ -3048,7 +3054,9 @@
       </c>
       <c r="E24" s="55"/>
       <c r="F24" s="56"/>
-      <c r="G24" s="57"/>
+      <c r="G24" s="57" t="n">
+        <v>15250</v>
+      </c>
       <c r="H24" s="49"/>
       <c r="I24" s="71"/>
       <c r="K24" s="93"/>
@@ -3069,7 +3077,7 @@
       <c r="E25" s="55"/>
       <c r="F25" s="56"/>
       <c r="G25" s="57" t="n">
-        <v>15000</v>
+        <v>15200</v>
       </c>
       <c r="H25" s="49"/>
       <c r="I25" s="53"/>
@@ -3099,7 +3107,7 @@
       <c r="F27" s="60"/>
       <c r="G27" s="95" t="n">
         <f aca="false">SUM(G6:G26)</f>
-        <v>172000</v>
+        <v>298900</v>
       </c>
       <c r="H27" s="62"/>
       <c r="I27" s="84"/>
